--- a/data/trans_orig/P04B1_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente fresca durante el verano en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>286576</t>
+          <t>283883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329814</t>
+          <t>329800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290219</t>
+          <t>287459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>324617</t>
+          <t>322761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589630</t>
+          <t>588154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>644078</t>
+          <t>641273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172341</t>
+          <t>172355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215579</t>
+          <t>218272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121479</t>
+          <t>123335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155877</t>
+          <t>158637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304173</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358621</t>
+          <t>360097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>279644</t>
+          <t>278480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>318616</t>
+          <t>318689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230918</t>
+          <t>229705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263303</t>
+          <t>261486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>520597</t>
+          <t>520287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>571165</t>
+          <t>573056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>133524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172569</t>
+          <t>173733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119277</t>
+          <t>121094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151662</t>
+          <t>152875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>263628</t>
+          <t>261737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314196</t>
+          <t>314506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>422907</t>
+          <t>420276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>612821</t>
+          <t>608652</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91229</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111515</t>
+          <t>111725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>520890</t>
+          <t>520964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>742487</t>
+          <t>741850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55443</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245357</t>
+          <t>247988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54740</t>
+          <t>54530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75026</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313629</t>
+          <t>313555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>640562</t>
+          <t>636673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>704154</t>
+          <t>703618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>662783</t>
+          <t>664327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>851584</t>
+          <t>850715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1328191</t>
+          <t>1326426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1615857</t>
+          <t>1576346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329886</t>
+          <t>330422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>393478</t>
+          <t>397367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126348</t>
+          <t>127217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315149</t>
+          <t>313605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396115</t>
+          <t>435626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683781</t>
+          <t>685546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>272734</t>
+          <t>272744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317494</t>
+          <t>316597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>477650</t>
+          <t>477897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>599851</t>
+          <t>608298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>773745</t>
+          <t>770712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>912943</t>
+          <t>916979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156522</t>
+          <t>157419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201282</t>
+          <t>201272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240864</t>
+          <t>232417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363065</t>
+          <t>362818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401788</t>
+          <t>397752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540986</t>
+          <t>544019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138562</t>
+          <t>136992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>183416</t>
+          <t>185003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>430002</t>
+          <t>427997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>482195</t>
+          <t>479985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>586023</t>
+          <t>583670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>654721</t>
+          <t>652757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>55340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>103351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279176</t>
+          <t>281386</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331369</t>
+          <t>333374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346992</t>
+          <t>348956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415690</t>
+          <t>418043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2145987</t>
+          <t>2148948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2485476</t>
+          <t>2537161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2266729</t>
+          <t>2260959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2607211</t>
+          <t>2580065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4446539</t>
+          <t>4465933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4944546</t>
+          <t>4995425</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>885554</t>
+          <t>833869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1225043</t>
+          <t>1222082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>967738</t>
+          <t>994884</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1308220</t>
+          <t>1313990</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2001433</t>
+          <t>1950554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2499440</t>
+          <t>2480046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>308922</t>
+          <t>335070</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>283883</t>
+          <t>312010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329800</t>
+          <t>358922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>307164</t>
+          <t>328998</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>287459</t>
+          <t>309003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>322761</t>
+          <t>344468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>616086</t>
+          <t>664068</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>588154</t>
+          <t>634716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>641273</t>
+          <t>693689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>193233</t>
+          <t>212560</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172355</t>
+          <t>188708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>235620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>157989</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123335</t>
+          <t>142519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158637</t>
+          <t>177984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>332165</t>
+          <t>370548</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306978</t>
+          <t>340927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>360097</t>
+          <t>399900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>502155</t>
+          <t>547630</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502155</t>
+          <t>547630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502155</t>
+          <t>547630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446096</t>
+          <t>486987</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446096</t>
+          <t>486987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446096</t>
+          <t>486987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>948251</t>
+          <t>1034616</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>948251</t>
+          <t>1034616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948251</t>
+          <t>1034616</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>299015</t>
+          <t>315117</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278480</t>
+          <t>293378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>318689</t>
+          <t>335989</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>246772</t>
+          <t>273368</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>229705</t>
+          <t>255292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>261486</t>
+          <t>288810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>545787</t>
+          <t>588485</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>520287</t>
+          <t>561838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573056</t>
+          <t>616492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>153198</t>
+          <t>168095</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133524</t>
+          <t>147223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173733</t>
+          <t>189834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>135808</t>
+          <t>149775</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121094</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152875</t>
+          <t>167851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>289006</t>
+          <t>317870</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>261737</t>
+          <t>289863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>314506</t>
+          <t>344517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>517554</t>
+          <t>301638</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>420276</t>
+          <t>280304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>608652</t>
+          <t>322374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101325</t>
+          <t>112894</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90884</t>
+          <t>100474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111725</t>
+          <t>123095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>618879</t>
+          <t>414532</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>520964</t>
+          <t>390653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>741850</t>
+          <t>438162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>150710</t>
+          <t>169974</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59612</t>
+          <t>149238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247988</t>
+          <t>191308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>73896</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54530</t>
+          <t>63695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>86316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>215640</t>
+          <t>243870</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92669</t>
+          <t>220240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313555</t>
+          <t>267749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>672497</t>
+          <t>715964</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>636673</t>
+          <t>678891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>703618</t>
+          <t>747978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>736737</t>
+          <t>582236</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>664327</t>
+          <t>556249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>850715</t>
+          <t>606409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1409234</t>
+          <t>1298200</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1326426</t>
+          <t>1254409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1576346</t>
+          <t>1340058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>361543</t>
+          <t>414879</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330422</t>
+          <t>382865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397367</t>
+          <t>451952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>241195</t>
+          <t>278007</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127217</t>
+          <t>253834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313605</t>
+          <t>303994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>602738</t>
+          <t>692886</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435626</t>
+          <t>651028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685546</t>
+          <t>736677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034040</t>
+          <t>1130843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034040</t>
+          <t>1130843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034040</t>
+          <t>1130843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011972</t>
+          <t>1991086</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011972</t>
+          <t>1991086</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011972</t>
+          <t>1991086</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>294712</t>
+          <t>341515</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>272744</t>
+          <t>318242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316597</t>
+          <t>369179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>523887</t>
+          <t>459763</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>477897</t>
+          <t>436522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>608298</t>
+          <t>485879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>818600</t>
+          <t>801277</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>770712</t>
+          <t>766441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>916979</t>
+          <t>838143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>179304</t>
+          <t>225367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157419</t>
+          <t>197703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201272</t>
+          <t>248640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>316828</t>
+          <t>370379</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232417</t>
+          <t>344263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362818</t>
+          <t>393620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>496131</t>
+          <t>595747</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397752</t>
+          <t>558881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544019</t>
+          <t>630583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314731</t>
+          <t>1397024</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314731</t>
+          <t>1397024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314731</t>
+          <t>1397024</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>161760</t>
+          <t>144852</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>136992</t>
+          <t>121558</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>185003</t>
+          <t>166199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>454972</t>
+          <t>490662</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>427997</t>
+          <t>463476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>479985</t>
+          <t>517533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>616732</t>
+          <t>635514</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>583670</t>
+          <t>597703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>652757</t>
+          <t>673532</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>62,37%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>78583</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>114027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>306399</t>
+          <t>353619</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>281386</t>
+          <t>326748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333374</t>
+          <t>380805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>384981</t>
+          <t>444352</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>348956</t>
+          <t>406334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418043</t>
+          <t>482163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2254461</t>
+          <t>2154155</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2148948</t>
+          <t>2093875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2537161</t>
+          <t>2214406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2370857</t>
+          <t>2247921</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2260959</t>
+          <t>2201038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2580065</t>
+          <t>2303068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4625317</t>
+          <t>4402077</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4465933</t>
+          <t>4323636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4995425</t>
+          <t>4485245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1116569</t>
+          <t>1281608</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>833869</t>
+          <t>1221357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1222082</t>
+          <t>1341888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1204092</t>
+          <t>1383665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>994884</t>
+          <t>1328518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1313990</t>
+          <t>1430548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2320662</t>
+          <t>2665272</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1950554</t>
+          <t>2582104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2480046</t>
+          <t>2743713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371030</t>
+          <t>3435763</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371030</t>
+          <t>3435763</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371030</t>
+          <t>3435763</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574949</t>
+          <t>3631586</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574949</t>
+          <t>3631586</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574949</t>
+          <t>3631586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945979</t>
+          <t>7067349</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945979</t>
+          <t>7067349</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945979</t>
+          <t>7067349</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
